--- a/output/pdf_financials_xlsx/MOO.xlsx
+++ b/output/pdf_financials_xlsx/MOO.xlsx
@@ -802,19 +802,19 @@
         <v>-0.063892</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.291818</v>
+        <v>-3.291818</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.377313</v>
+        <v>-1.377313</v>
       </c>
     </row>
     <row r="17">
@@ -926,19 +926,19 @@
         <v>-0.063892</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.291818</v>
+        <v>-3.291818</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.377313</v>
+        <v>-1.377313</v>
       </c>
     </row>
     <row r="21">
@@ -1001,19 +1001,19 @@
         <v>-0.063892</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.291818</v>
+        <v>-3.291818</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.377313</v>
+        <v>-1.377313</v>
       </c>
     </row>
     <row r="24">
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>14.362918</v>
+        <v>-14.362918</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>32.91818</v>
+        <v>-32.91818</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>32.793167</v>
+        <v>-32.793167</v>
       </c>
     </row>
     <row r="27">
@@ -1111,19 +1111,19 @@
         <v>-0.063892</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.291818</v>
+        <v>-3.291818</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.377313</v>
+        <v>-1.377313</v>
       </c>
     </row>
     <row r="28">
@@ -1161,19 +1161,19 @@
         <v>-0.063892</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.2975</v>
+        <v>-3.286136</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.391422</v>
+        <v>-1.363204</v>
       </c>
     </row>
     <row r="30">
@@ -1223,19 +1223,19 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.035846</v>
+        <v>0.022243</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.035846</v>
+        <v>0.369653</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -6102,7 +6102,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -9548,16 +9552,16 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>4.03598</v>
+        <v>-4.03598</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>3.291818</v>
+        <v>-3.291818</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>1.377313</v>
+        <v>-1.377313</v>
       </c>
     </row>
     <row r="118">
@@ -10271,10 +10275,10 @@
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.055255</v>
+        <v>-0.055255</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -10672,10 +10676,10 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.063892</v>
+        <v>-0.063892</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.029204</v>
+        <v>-0.029204</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MOO.xlsx
+++ b/output/pdf_financials_xlsx/MOO.xlsx
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023775</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.104605</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-1.098343</v>
       </c>
     </row>
     <row r="13">
@@ -1117,13 +1117,13 @@
         <v>-0.055255</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.03598</v>
+        <v>-4.012205</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.291818</v>
+        <v>-2.187213</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.377313</v>
+        <v>-0.27897</v>
       </c>
     </row>
     <row r="28">
@@ -1167,13 +1167,13 @@
         <v>-0.055255</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.03598</v>
+        <v>-4.012205</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.286136</v>
+        <v>-2.181531</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.363204</v>
+        <v>-0.264861</v>
       </c>
     </row>
     <row r="30">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOO.xlsx
+++ b/output/pdf_financials_xlsx/MOO.xlsx
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1.9e-05</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1.9e-05</v>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0.055255</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>2.248282</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.014109</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>2.234173</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>2.43773</v>
@@ -2177,16 +2177,16 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.017237</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.158598</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.111033</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.21582</v>
       </c>
     </row>
     <row r="65">
@@ -2299,10 +2299,10 @@
         <v>0.009423000000000001</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.006075</v>
+        <v>3.117108</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1.225262</v>
+        <v>1.441082</v>
       </c>
     </row>
     <row r="69">
@@ -2502,10 +2502,10 @@
         <v>0.266885</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>5.179443</v>
+        <v>4.06841</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.8691</v>
+        <v>2.65328</v>
       </c>
     </row>
     <row r="76">
@@ -10176,7 +10176,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>2.5e-05</v>
       </c>
